--- a/03_Prompting/outputs/GPT/RESULT_f-droid_gpt-4o_persona_fewshot_cot.xlsx
+++ b/03_Prompting/outputs/GPT/RESULT_f-droid_gpt-4o_persona_fewshot_cot.xlsx
@@ -782,7 +782,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -9182,7 +9182,7 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -10848,7 +10848,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -11103,7 +11103,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -13500,7 +13500,7 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15268,7 +15268,7 @@
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15353,7 +15353,7 @@
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -15591,7 +15591,7 @@
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15693,7 +15693,7 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -16101,7 +16101,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17155,7 +17155,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17988,7 +17988,7 @@
       </c>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18328,7 +18328,7 @@
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -20742,7 +20742,7 @@
       </c>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -24931,7 +24931,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -25220,7 +25220,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="C1561" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -39960,7 +39960,7 @@
       </c>
       <c r="C2325" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -45281,7 +45281,7 @@
       </c>
       <c r="C2638" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -48443,7 +48443,7 @@
       </c>
       <c r="C2824" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -48786,7 +48786,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6413234776487152</v>
+        <v>0.6332277367124252</v>
       </c>
     </row>
     <row r="3">
@@ -48796,7 +48796,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5218768131033459</v>
+        <v>0.5066590451557854</v>
       </c>
     </row>
     <row r="4">
@@ -48806,7 +48806,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5586361035303363</v>
+        <v>0.5450958194506093</v>
       </c>
     </row>
     <row r="5">
@@ -48816,7 +48816,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.76801928884152</v>
+        <v>0.7565126845891708</v>
       </c>
     </row>
     <row r="6">
@@ -48826,7 +48826,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5781194957763094</v>
+        <v>0.5687739267176224</v>
       </c>
     </row>
     <row r="7">
@@ -48836,7 +48836,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>671.6110211590003</v>
+        <v>1512.250355558004</v>
       </c>
     </row>
     <row r="8">
@@ -48846,7 +48846,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2363995146634989</v>
+        <v>0.5322950917134827</v>
       </c>
     </row>
   </sheetData>
